--- a/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
@@ -1616,13 +1616,13 @@
         <v>20</v>
       </c>
       <c r="J2" t="n">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="K2" t="n">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="L2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M2" t="n">
         <v>100</v>
@@ -1967,7 +1967,7 @@
         <v>169</v>
       </c>
       <c r="DW2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="DX2" t="n">
         <v>11</v>
@@ -2111,16 +2111,16 @@
         <v>0.4848484848484849</v>
       </c>
       <c r="FS2" t="n">
-        <v>15.73092307692308</v>
+        <v>15.68266871165644</v>
       </c>
       <c r="FT2" t="n">
-        <v>15.21424196018377</v>
+        <v>15.26098310291859</v>
       </c>
       <c r="FU2" t="n">
-        <v>14.79015384615385</v>
+        <v>14.74478527607362</v>
       </c>
       <c r="FV2" t="n">
-        <v>14.64226646248086</v>
+        <v>14.68725038402458</v>
       </c>
       <c r="FW2" t="n">
         <v>0.1983739837398374</v>
@@ -2264,7 +2264,7 @@
         <v>26.05077399380805</v>
       </c>
       <c r="HR2" t="n">
-        <v>0.2338461538461538</v>
+        <v>0.2346625766871166</v>
       </c>
       <c r="HS2" t="inlineStr"/>
       <c r="HT2" t="inlineStr"/>
@@ -2311,16 +2311,16 @@
         <v>-109</v>
       </c>
       <c r="J3" t="n">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="K3" t="n">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="L3" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="M3" t="n">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N3" t="n">
         <v>113</v>
@@ -2660,7 +2660,7 @@
         <v>234</v>
       </c>
       <c r="DW3" t="n">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="DX3" t="n">
         <v>21</v>
@@ -2804,16 +2804,16 @@
         <v>0.5581395348837209</v>
       </c>
       <c r="FS3" t="n">
-        <v>15.18617332035054</v>
+        <v>15.11259689922481</v>
       </c>
       <c r="FT3" t="n">
-        <v>15.5099324975892</v>
+        <v>15.58507751937984</v>
       </c>
       <c r="FU3" t="n">
-        <v>14.62259006815969</v>
+        <v>14.55174418604651</v>
       </c>
       <c r="FV3" t="n">
-        <v>14.65737704918033</v>
+        <v>14.72839147286822</v>
       </c>
       <c r="FW3" t="n">
         <v>0.2579234972677595</v>
@@ -2957,7 +2957,7 @@
         <v>25.82742382271468</v>
       </c>
       <c r="HR3" t="n">
-        <v>0.2112950340798442</v>
+        <v>0.2141472868217054</v>
       </c>
       <c r="HS3" t="n">
         <v>1</v>
@@ -3008,16 +3008,16 @@
         <v>-55</v>
       </c>
       <c r="J4" t="n">
-        <v>1732</v>
+        <v>1739</v>
       </c>
       <c r="K4" t="n">
-        <v>1745</v>
+        <v>1738</v>
       </c>
       <c r="L4" t="n">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="M4" t="n">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="N4" t="n">
         <v>220</v>
@@ -3357,7 +3357,7 @@
         <v>665</v>
       </c>
       <c r="DW4" t="n">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="DX4" t="n">
         <v>41</v>
@@ -3501,16 +3501,16 @@
         <v>0.5274725274725275</v>
       </c>
       <c r="FS4" t="n">
-        <v>15.23158198614319</v>
+        <v>15.17027027027027</v>
       </c>
       <c r="FT4" t="n">
-        <v>15.10538681948424</v>
+        <v>15.1662255466053</v>
       </c>
       <c r="FU4" t="n">
-        <v>14.47448036951501</v>
+        <v>14.41621621621622</v>
       </c>
       <c r="FV4" t="n">
-        <v>14.38103151862464</v>
+        <v>14.43895281933257</v>
       </c>
       <c r="FW4" t="n">
         <v>0.2540431266846361</v>
@@ -3654,7 +3654,7 @@
         <v>25.57434402332362</v>
       </c>
       <c r="HR4" t="n">
-        <v>0.3366050808314088</v>
+        <v>0.3387004025301897</v>
       </c>
       <c r="HS4" t="inlineStr"/>
       <c r="HT4" t="inlineStr"/>
@@ -3703,16 +3703,16 @@
         <v>-69</v>
       </c>
       <c r="J5" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K5" t="n">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L5" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M5" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="N5" t="n">
         <v>50</v>
@@ -4042,7 +4042,7 @@
         <v>104</v>
       </c>
       <c r="DW5" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="DX5" t="n">
         <v>16</v>
@@ -4186,16 +4186,16 @@
         <v>0.4545454545454545</v>
       </c>
       <c r="FS5" t="n">
-        <v>14.94803149606299</v>
+        <v>14.86997389033943</v>
       </c>
       <c r="FT5" t="n">
-        <v>15.09015544041451</v>
+        <v>15.16875</v>
       </c>
       <c r="FU5" t="n">
-        <v>14.11496062992126</v>
+        <v>14.04125326370757</v>
       </c>
       <c r="FV5" t="n">
-        <v>14.37098445595855</v>
+        <v>14.44583333333333</v>
       </c>
       <c r="FW5" t="n">
         <v>0.1849710982658959</v>
@@ -4339,7 +4339,7 @@
         <v>25.92666666666667</v>
       </c>
       <c r="HR5" t="n">
-        <v>0.2493438320209974</v>
+        <v>0.2532637075718016</v>
       </c>
       <c r="HS5" t="inlineStr"/>
       <c r="HT5" t="inlineStr"/>
@@ -4386,19 +4386,19 @@
         <v>283</v>
       </c>
       <c r="J6" t="n">
-        <v>1811</v>
+        <v>1821</v>
       </c>
       <c r="K6" t="n">
-        <v>1833</v>
+        <v>1823</v>
       </c>
       <c r="L6" t="n">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="M6" t="n">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="N6" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O6" t="n">
         <v>3644</v>
@@ -4735,7 +4735,7 @@
         <v>648</v>
       </c>
       <c r="DW6" t="n">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="DX6" t="n">
         <v>45</v>
@@ -4879,16 +4879,16 @@
         <v>0.6463414634146342</v>
       </c>
       <c r="FS6" t="n">
-        <v>15.9941468801767</v>
+        <v>15.9063152114223</v>
       </c>
       <c r="FT6" t="n">
-        <v>14.21418439716312</v>
+        <v>14.29215578716402</v>
       </c>
       <c r="FU6" t="n">
-        <v>15.29094422970734</v>
+        <v>15.20697419000549</v>
       </c>
       <c r="FV6" t="n">
-        <v>13.66541189307147</v>
+        <v>13.74037301151947</v>
       </c>
       <c r="FW6" t="n">
         <v>0.3292383292383292</v>
@@ -5032,7 +5032,7 @@
         <v>25.18421875</v>
       </c>
       <c r="HR6" t="n">
-        <v>0.2816123688569851</v>
+        <v>0.28555738605162</v>
       </c>
       <c r="HS6" t="n">
         <v>2</v>
@@ -5083,16 +5083,16 @@
         <v>-15</v>
       </c>
       <c r="J7" t="n">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K7" t="n">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L7" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M7" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="N7" t="n">
         <v>84</v>
@@ -5420,7 +5420,7 @@
         <v>152</v>
       </c>
       <c r="DW7" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="DX7" t="n">
         <v>15</v>
@@ -5564,16 +5564,16 @@
         <v>0.53125</v>
       </c>
       <c r="FS7" t="n">
-        <v>15.7136690647482</v>
+        <v>15.65734767025089</v>
       </c>
       <c r="FT7" t="n">
-        <v>15.76327985739751</v>
+        <v>15.81967799642218</v>
       </c>
       <c r="FU7" t="n">
-        <v>14.93615107913669</v>
+        <v>14.8826164874552</v>
       </c>
       <c r="FV7" t="n">
-        <v>15.00249554367202</v>
+        <v>15.05617173524151</v>
       </c>
       <c r="FW7" t="n">
         <v>0.2771317829457364</v>
@@ -5717,7 +5717,7 @@
         <v>25.68793969849246</v>
       </c>
       <c r="HR7" t="n">
-        <v>0.2661870503597122</v>
+        <v>0.2688172043010753</v>
       </c>
       <c r="HS7" t="inlineStr"/>
       <c r="HT7" t="n">
@@ -5766,16 +5766,16 @@
         <v>-33</v>
       </c>
       <c r="J8" t="n">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="K8" t="n">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="L8" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="M8" t="n">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="N8" t="n">
         <v>92</v>
@@ -6109,7 +6109,7 @@
         <v>206</v>
       </c>
       <c r="DW8" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="DX8" t="n">
         <v>28</v>
@@ -6253,16 +6253,16 @@
         <v>0.5952380952380952</v>
       </c>
       <c r="FS8" t="n">
-        <v>15.26939393939394</v>
+        <v>15.15458646616541</v>
       </c>
       <c r="FT8" t="n">
-        <v>15.13843843843844</v>
+        <v>15.25295007564297</v>
       </c>
       <c r="FU8" t="n">
-        <v>14.46181818181818</v>
+        <v>14.35308270676692</v>
       </c>
       <c r="FV8" t="n">
-        <v>14.32702702702703</v>
+        <v>14.43540090771558</v>
       </c>
       <c r="FW8" t="n">
         <v>0.2333901192504259</v>
@@ -6406,7 +6406,7 @@
         <v>25.94033613445378</v>
       </c>
       <c r="HR8" t="n">
-        <v>0.3227272727272728</v>
+        <v>0.324812030075188</v>
       </c>
       <c r="HS8" t="n">
         <v>2</v>
@@ -6457,16 +6457,16 @@
         <v>-62</v>
       </c>
       <c r="J9" t="n">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K9" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="L9" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="M9" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="N9" t="n">
         <v>70</v>
@@ -6798,7 +6798,7 @@
         <v>135</v>
       </c>
       <c r="DW9" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="DX9" t="n">
         <v>8</v>
@@ -6942,16 +6942,16 @@
         <v>0.7083333333333334</v>
       </c>
       <c r="FS9" t="n">
-        <v>14.9398322851153</v>
+        <v>14.84645833333333</v>
       </c>
       <c r="FT9" t="n">
-        <v>15.02830578512397</v>
+        <v>15.12203742203742</v>
       </c>
       <c r="FU9" t="n">
-        <v>14.03396226415094</v>
+        <v>13.94625</v>
       </c>
       <c r="FV9" t="n">
-        <v>14.32148760330578</v>
+        <v>14.41081081081081</v>
       </c>
       <c r="FW9" t="n">
         <v>0.3109619686800895</v>
@@ -7093,7 +7093,7 @@
         <v>25.15052083333333</v>
       </c>
       <c r="HR9" t="n">
-        <v>0.2620545073375262</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="HS9" t="n">
         <v>2</v>
@@ -7146,19 +7146,19 @@
         <v>173</v>
       </c>
       <c r="J10" t="n">
-        <v>2254</v>
+        <v>2262</v>
       </c>
       <c r="K10" t="n">
-        <v>2270</v>
+        <v>2262</v>
       </c>
       <c r="L10" t="n">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="M10" t="n">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="N10" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O10" t="n">
         <v>4524</v>
@@ -7495,7 +7495,7 @@
         <v>868</v>
       </c>
       <c r="DW10" t="n">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="DX10" t="n">
         <v>60</v>
@@ -7639,16 +7639,16 @@
         <v>0.525</v>
       </c>
       <c r="FS10" t="n">
-        <v>14.3550133096717</v>
+        <v>14.30424403183024</v>
       </c>
       <c r="FT10" t="n">
-        <v>15.1911013215859</v>
+        <v>15.2448275862069</v>
       </c>
       <c r="FU10" t="n">
-        <v>13.7698314108252</v>
+        <v>13.7211317418214</v>
       </c>
       <c r="FV10" t="n">
-        <v>14.42832599118943</v>
+        <v>14.47935455349249</v>
       </c>
       <c r="FW10" t="n">
         <v>0.3229532898041185</v>
@@ -7792,7 +7792,7 @@
         <v>25.23978102189781</v>
       </c>
       <c r="HR10" t="n">
-        <v>0.3558118899733806</v>
+        <v>0.3580901856763926</v>
       </c>
       <c r="HS10" t="n">
         <v>9</v>
@@ -7845,16 +7845,16 @@
         <v>-49</v>
       </c>
       <c r="J11" t="n">
+        <v>936</v>
+      </c>
+      <c r="K11" t="n">
         <v>933</v>
       </c>
-      <c r="K11" t="n">
-        <v>936</v>
-      </c>
       <c r="L11" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="M11" t="n">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="N11" t="n">
         <v>111</v>
@@ -8194,7 +8194,7 @@
         <v>232</v>
       </c>
       <c r="DW11" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="DX11" t="n">
         <v>20</v>
@@ -8334,16 +8334,16 @@
         <v>0.48</v>
       </c>
       <c r="FS11" t="n">
-        <v>16.09024651661308</v>
+        <v>16.03867521367522</v>
       </c>
       <c r="FT11" t="n">
-        <v>15.05106837606838</v>
+        <v>15.0994640943194</v>
       </c>
       <c r="FU11" t="n">
-        <v>15.43226152197213</v>
+        <v>15.38279914529915</v>
       </c>
       <c r="FV11" t="n">
-        <v>14.37884615384615</v>
+        <v>14.42508038585209</v>
       </c>
       <c r="FW11" t="n">
         <v>0.2847938144329897</v>
@@ -8487,7 +8487,7 @@
         <v>25.87592592592593</v>
       </c>
       <c r="HR11" t="n">
-        <v>0.2357984994640943</v>
+        <v>0.2382478632478632</v>
       </c>
       <c r="HS11" t="inlineStr"/>
       <c r="HT11" t="n">
@@ -8536,16 +8536,16 @@
         <v>-70</v>
       </c>
       <c r="J12" t="n">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="K12" t="n">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="L12" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="M12" t="n">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="N12" t="n">
         <v>171</v>
@@ -8883,7 +8883,7 @@
         <v>426</v>
       </c>
       <c r="DW12" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="DX12" t="n">
         <v>37</v>
@@ -9027,16 +9027,16 @@
         <v>0.6585365853658537</v>
       </c>
       <c r="FS12" t="n">
-        <v>14.72702251876564</v>
+        <v>14.69026622296173</v>
       </c>
       <c r="FT12" t="n">
-        <v>13.9919701986755</v>
+        <v>14.02680497925311</v>
       </c>
       <c r="FU12" t="n">
-        <v>13.96605504587156</v>
+        <v>13.93119800332779</v>
       </c>
       <c r="FV12" t="n">
-        <v>13.49180463576159</v>
+        <v>13.52539419087137</v>
       </c>
       <c r="FW12" t="n">
         <v>0.3193812556869882</v>
@@ -9180,7 +9180,7 @@
         <v>25.32085561497326</v>
       </c>
       <c r="HR12" t="n">
-        <v>0.3160967472894078</v>
+        <v>0.3178036605657238</v>
       </c>
       <c r="HS12" t="n">
         <v>1</v>
@@ -9233,19 +9233,19 @@
         <v>-27</v>
       </c>
       <c r="J13" t="n">
+        <v>595</v>
+      </c>
+      <c r="K13" t="n">
         <v>591</v>
       </c>
-      <c r="K13" t="n">
-        <v>595</v>
-      </c>
       <c r="L13" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="M13" t="n">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="N13" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O13" t="n">
         <v>1186</v>
@@ -9568,7 +9568,7 @@
         <v>243</v>
       </c>
       <c r="DW13" t="n">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="DX13" t="n">
         <v>9</v>
@@ -9706,16 +9706,16 @@
         <v>0.44</v>
       </c>
       <c r="FS13" t="n">
-        <v>14.55600676818951</v>
+        <v>14.4581512605042</v>
       </c>
       <c r="FT13" t="n">
-        <v>14.58386554621849</v>
+        <v>14.68257191201354</v>
       </c>
       <c r="FU13" t="n">
-        <v>14.01319796954315</v>
+        <v>13.91899159663866</v>
       </c>
       <c r="FV13" t="n">
-        <v>13.75378151260504</v>
+        <v>13.84686971235195</v>
       </c>
       <c r="FW13" t="n">
         <v>0.2649402390438247</v>
@@ -9855,7 +9855,7 @@
         <v>25.34663212435233</v>
       </c>
       <c r="HR13" t="n">
-        <v>0.3705583756345178</v>
+        <v>0.3747899159663866</v>
       </c>
       <c r="HS13" t="n">
         <v>1</v>
@@ -9904,19 +9904,19 @@
         <v>-105</v>
       </c>
       <c r="J14" t="n">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="K14" t="n">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="L14" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M14" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N14" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O14" t="n">
         <v>1154</v>
@@ -10249,7 +10249,7 @@
         <v>162</v>
       </c>
       <c r="DW14" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="DX14" t="n">
         <v>23</v>
@@ -10393,16 +10393,16 @@
         <v>0.6206896551724138</v>
       </c>
       <c r="FS14" t="n">
-        <v>13.944</v>
+        <v>13.91979166666667</v>
       </c>
       <c r="FT14" t="n">
-        <v>15.99689119170985</v>
+        <v>16.02456747404844</v>
       </c>
       <c r="FU14" t="n">
-        <v>13.40121739130435</v>
+        <v>13.37795138888889</v>
       </c>
       <c r="FV14" t="n">
-        <v>15.40880829015544</v>
+        <v>15.43546712802768</v>
       </c>
       <c r="FW14" t="n">
         <v>0.2806324110671937</v>
@@ -10542,7 +10542,7 @@
         <v>25.12247706422018</v>
       </c>
       <c r="HR14" t="n">
-        <v>0.2643478260869565</v>
+        <v>0.265625</v>
       </c>
       <c r="HS14" t="inlineStr"/>
       <c r="HT14" t="inlineStr"/>
@@ -11282,16 +11282,16 @@
         <v>107</v>
       </c>
       <c r="J16" t="n">
-        <v>1451</v>
+        <v>1460</v>
       </c>
       <c r="K16" t="n">
-        <v>1467</v>
+        <v>1458</v>
       </c>
       <c r="L16" t="n">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="M16" t="n">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="N16" t="n">
         <v>195</v>
@@ -11633,7 +11633,7 @@
         <v>488</v>
       </c>
       <c r="DW16" t="n">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="DX16" t="n">
         <v>36</v>
@@ -11777,16 +11777,16 @@
         <v>0.5507246376811594</v>
       </c>
       <c r="FS16" t="n">
-        <v>15.04521019986216</v>
+        <v>14.95246575342466</v>
       </c>
       <c r="FT16" t="n">
-        <v>14.97573278800273</v>
+        <v>15.0681755829904</v>
       </c>
       <c r="FU16" t="n">
-        <v>14.35506547208821</v>
+        <v>14.26657534246575</v>
       </c>
       <c r="FV16" t="n">
-        <v>14.34219495569189</v>
+        <v>14.43072702331962</v>
       </c>
       <c r="FW16" t="n">
         <v>0.237987987987988</v>
@@ -11930,7 +11930,7 @@
         <v>25.28784029038113</v>
       </c>
       <c r="HR16" t="n">
-        <v>0.275671950379049</v>
+        <v>0.2780821917808219</v>
       </c>
       <c r="HS16" t="inlineStr"/>
       <c r="HT16" t="inlineStr"/>
@@ -11979,19 +11979,19 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="K17" t="n">
-        <v>1328</v>
+        <v>1324</v>
       </c>
       <c r="L17" t="n">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="M17" t="n">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="N17" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O17" t="n">
         <v>2645</v>
@@ -12330,7 +12330,7 @@
         <v>437</v>
       </c>
       <c r="DW17" t="n">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="DX17" t="n">
         <v>46</v>
@@ -12472,16 +12472,16 @@
         <v>0.5392156862745098</v>
       </c>
       <c r="FS17" t="n">
-        <v>15.57623386484434</v>
+        <v>15.52906888720666</v>
       </c>
       <c r="FT17" t="n">
-        <v>15.14013554216867</v>
+        <v>15.18587613293051</v>
       </c>
       <c r="FU17" t="n">
-        <v>14.73720577069096</v>
+        <v>14.69258137774414</v>
       </c>
       <c r="FV17" t="n">
-        <v>14.33328313253012</v>
+        <v>14.37658610271903</v>
       </c>
       <c r="FW17" t="n">
         <v>0.2704778156996587</v>
@@ -12625,7 +12625,7 @@
         <v>25.7578947368421</v>
       </c>
       <c r="HR17" t="n">
-        <v>0.3120728929384966</v>
+        <v>0.3141559424678274</v>
       </c>
       <c r="HS17" t="n">
         <v>1</v>
